--- a/Economie_du_developpement.xlsx
+++ b/Economie_du_developpement.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Developpement économique</t>
+          <t>Développement économique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Developpement économique</t>
+          <t>Développement économique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Developpement économique</t>
+          <t>Développement économique</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Developpement économique</t>
+          <t>Développement économique</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Developpement économique</t>
+          <t>Développement économique</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1957,10 +1957,8 @@
           <t>OUATTARA Somon Abiba</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0779135993</t>
-        </is>
+      <c r="E31" t="n">
+        <v>779135993</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2010,10 +2008,8 @@
           <t>MEYER Sopie Laeticia</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0779135993</t>
-        </is>
+      <c r="E32" t="n">
+        <v>779135993</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2112,10 +2108,8 @@
           <t>AYEREBI Tanoa Olivia Sévérine Hermine</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0778963064</t>
-        </is>
+      <c r="E34" t="n">
+        <v>778963064</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2165,10 +2159,8 @@
           <t>ESMEL Amari Evrard Ulrich</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0152521053</t>
-        </is>
+      <c r="E35" t="n">
+        <v>152521053</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2218,10 +2210,8 @@
           <t>MIAKO Jean Yves Arnold</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0103926375</t>
-        </is>
+      <c r="E36" t="n">
+        <v>103926375</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
